--- a/data/google_news_dedup_audit_16_0426_UTC.xlsx
+++ b/data/google_news_dedup_audit_16_0426_UTC.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,631 +445,169 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7896461486816406</v>
+        <v>0.8500741124153137</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Royal Mail delivery delays hit 3 Nuneaton postcode areas today — full list - Coventry Telegraph</t>
+          <t>A trick to get free delivery on Amazon | Money newsletter - MKFM</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Royal Mail delivery delays hit 3 Merseyside postcodes today — full list of affected areas - Liverpool Echo</t>
+          <t>A trick to get free delivery on Amazon | Money newsletter - This is the Coast</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7714263200759888</v>
+        <v>0.8340055346488953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Royal Mail delivery delays hit 3 Nuneaton postcode areas today — full list - Coventry Telegraph</t>
+          <t>A trick to get free delivery on Amazon | Money newsletter - MKFM</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Royal Mail delivery disruption hits 34 UK postcodes today as delays continue — full list - The Mirror</t>
+          <t>A trick to get free delivery on Amazon | Money newsletter - Roch Valley Radio</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6713812351226807</v>
+        <v>0.9909540414810181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Winn-Dixie delivery now available to Pensacola residents through Amazon - AOL.com</t>
+          <t>Tiental wagens beschadigd na explosie in Sint-Gillis: al tweede incident op enkele dagen tijd - GVA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Amazon and Winn-Dixie expand grocery delivery partnership, now reaching majority of Florida households - Alachua Chronicle</t>
+          <t>Tiental wagens beschadigd na explosie in Sint-Gillis: al tweede incident op enkele dagen tijd - Nieuwsblad</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6778314709663391</v>
+        <v>0.9940227270126343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Winn-Dixie delivery now available to Pensacola residents through Amazon - AOL.com</t>
+          <t>Tiental wagens beschadigd na explosie in Sint-Gillis: al tweede incident op enkele dagen tijd - GVA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Winn-Dixie and Amazon expand grocery delivery to most of Florida - Lakeland Ledger</t>
+          <t>Tiental wagens beschadigd na explosie in Sint-Gillis: al tweede incident op enkele dagen tijd - HBVL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6651057004928589</v>
+        <v>0.6202826499938965</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Winn-Dixie delivery now available to Pensacola residents through Amazon - AOL.com</t>
+          <t>Saint-Gilles : la rue de Bosnie touchée par une explosion - BX1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Amazon, Winn-Dixie Expand Florida Grocery Delivery - Store Brands</t>
+          <t>Une nouvelle fusillade a éclaté à Saint-Gilles - BruxellesToday</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7180513143539429</v>
+        <v>0.8008680939674377</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Winn-Dixie delivery now available to Pensacola residents through Amazon - AOL.com</t>
+          <t>Saint-Gilles : la rue de Bosnie touchée par une explosion - BX1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Winn-Dixie and Amazon Expand Same-Day Grocery Delivery to West Palm Beach - National Today</t>
+          <t>Après deux fusillades, une explosion dans la rue de Bosnie à Saint-Gilles - BruxellesToday</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8815547227859497</v>
+        <v>0.7041065692901611</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Verdachte (37) van schietpartij op Battelsesteenweg blijft in de cel, zijn neef (19) vrijgelaten: ruzie ontstond in hotel - GVA</t>
+          <t>London Tube and Bus strike dates, routes and times for April 2026 - lbc.co.uk</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Verdachten schietpartij op Battelsesteenweg blijven aangehouden: ruzie ontstond in hotel - Nieuwsblad</t>
+          <t>Tube and bus strikes set to bring four days of travel chaos next week - London Evening Standard</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7747411727905273</v>
+        <v>0.7007162570953369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Opnieuw schietpartij op Turkse school, meerdere doden - Welingelichte Kringen</t>
+          <t>Sciopero trasporti in arrivo: bus fermi a Milano, Monza Brianza, Lodi e Pavia. Le fasce orarie - MilanoToday</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nieuwe schietpartij op school in Turkije: drie leerlingen en leraar omgekomen, ook twintig gewonden - HLN</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>26</v>
-      </c>
-      <c r="B10" t="n">
-        <v>30</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.7941498756408691</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Opnieuw schietpartij op Turkse school, meerdere doden - Welingelichte Kringen</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Nieuwe schietpartij op school in Turkije - HLN</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>37</v>
-      </c>
-      <c r="B11" t="n">
-        <v>38</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.4419896602630615</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Une nouvelle fusillade a éclaté à Saint-Gilles - BruxellesToday</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Patrick Bruel accusé d’agression sexuelle dans les locaux de la RTBF: une enquête ouverte en Belgique - 7sur7.be</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>37</v>
-      </c>
-      <c r="B12" t="n">
-        <v>39</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.5973263382911682</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Une nouvelle fusillade a éclaté à Saint-Gilles - BruxellesToday</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Patrick Bruel : une enquête ouverte à Bruxelles pour des faits présumés d’agression sexuelles - Anadolu Ajansı</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>37</v>
-      </c>
-      <c r="B13" t="n">
-        <v>40</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.4407565593719482</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Une nouvelle fusillade a éclaté à Saint-Gilles - BruxellesToday</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>La justice belge ouvre une enquête après une plainte pour agression sexuelle contre le chanteur Patrick Bruel - francebleu.fr</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>37</v>
-      </c>
-      <c r="B14" t="n">
-        <v>41</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.495325893163681</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Une nouvelle fusillade a éclaté à Saint-Gilles - BruxellesToday</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>“Tout le monde savait que Patrick Bruel était problématique” : une enquête ouverte en Belgique pour agression sexuelle - La Montagne</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>37</v>
-      </c>
-      <c r="B15" t="n">
-        <v>42</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.730047345161438</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Une nouvelle fusillade a éclaté à Saint-Gilles - BruxellesToday</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Une enquête ouverte en Belgique visant Patrick Bruel pour agression sexuelle dans les locaux de la RTBF - BruxellesToday</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>37</v>
-      </c>
-      <c r="B16" t="n">
-        <v>45</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.3817267715930939</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Une nouvelle fusillade a éclaté à Saint-Gilles - BruxellesToday</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Patrick Bruel accusé d’agression sexuelle : la justice belge ouvre une enquête - parismatch.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>43</v>
-      </c>
-      <c r="B17" t="n">
-        <v>44</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.8424919247627258</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>EN DIRECT - Patrick Bruel : Au lendemain de l’ouverture d’une enquête en France, une autre enquête j... - jeanmarcmorandini.com</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>URGENT : Au lendemain de l’annonce de l’ouverture d’une enquête en France, une autre enquête judic... - jeanmarcmorandini.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>56</v>
-      </c>
-      <c r="B18" t="n">
-        <v>57</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.8543760776519775</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Ronda Limburgo: La clásica en directo - Ciclo21</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Ronda Limburgo: Merlier ante el resucitado Gaviria - Ciclo21</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>58</v>
-      </c>
-      <c r="B19" t="n">
-        <v>60</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.6667683124542236</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Germany news: Lufthansa air crew strike after pilot walkout - DW.com</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Lufthansa Strike Wave to Last Through Friday as Pilots Call Another 48-Hour Walkout - Travel Market Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>58</v>
-      </c>
-      <c r="B20" t="n">
-        <v>61</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.7939114570617676</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Germany news: Lufthansa air crew strike after pilot walkout - DW.com</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>German pilots’ union announces further strikes at Lufthansa this week - Euronews.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>58</v>
-      </c>
-      <c r="B21" t="n">
-        <v>62</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.7624579668045044</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Germany news: Lufthansa air crew strike after pilot walkout - DW.com</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Lufthansa pilots to strike again for 2 more days - DW.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>58</v>
-      </c>
-      <c r="B22" t="n">
-        <v>63</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.7439532279968262</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Germany news: Lufthansa air crew strike after pilot walkout - DW.com</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>A new strike paralyzes Lufthansa flights in Germany this weekend - صوت الإمارات</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>67</v>
-      </c>
-      <c r="B23" t="n">
-        <v>68</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.7399535179138184</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Weltkriegs-Bombe in Neuburg gefunden - Pfaffenhofen Today</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Bombenfund in Neuburg: Weltkriegsbombe erfolgreich entschärft - HITRADIO RT1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>80</v>
-      </c>
-      <c r="B24" t="n">
-        <v>86</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.7326147556304932</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>London police refuses protest letter over ban of Nakba march - The New Arab</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Coalition in London vows Nakba march despite police rejection - The New Arab</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>82</v>
-      </c>
-      <c r="B25" t="n">
-        <v>83</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0.7186276912689209</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Tube and bus strikes set to bring four days of travel chaos next week - London Evening Standard</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Six days of tube strikes on the London Underground will start next week - Time Out</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>92</v>
-      </c>
-      <c r="B26" t="n">
-        <v>93</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.7244057655334473</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Remigrazione, Salvini a Milano con i patrioti - il manifesto</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>La Lega Abruzzo a Milano per la manifestazione dei Patrioti europei - News Town</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>92</v>
-      </c>
-      <c r="B27" t="n">
-        <v>102</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0.7148284912109375</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Remigrazione, Salvini a Milano con i patrioti - il manifesto</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Milano, Calenda a Salvini : Trasformista, per la manifestazione di sabato diventa europeista - Il Mattino</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>92</v>
-      </c>
-      <c r="B28" t="n">
-        <v>106</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.5766929984092712</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Remigrazione, Salvini a Milano con i patrioti - il manifesto</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Sesto San Giovanni, respinte le richieste per presidi di sicurezza: sabato manifestazione in piazza - Il Gazzettino Metropolitano</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>92</v>
-      </c>
-      <c r="B29" t="n">
-        <v>108</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0.6327123641967773</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Remigrazione, Salvini a Milano con i patrioti - il manifesto</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Lega Abruzzo, sabato a Milano per la manifestazione sulla sicurezza - ilpomeriggio.it</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>92</v>
-      </c>
-      <c r="B30" t="n">
-        <v>111</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0.6223834156990051</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Remigrazione, Salvini a Milano con i patrioti - il manifesto</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>La Lega presenta legge sull'immigrazione: stop al patrocinio gratuito, ricongiungimenti solo di primo grado e blocco navale - Polemica su evento a Milano - upday News</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>94</v>
-      </c>
-      <c r="B31" t="n">
-        <v>110</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0.7260531783103943</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Salvini: “Nessun Remigration Summit. Sabato a Milano una grande manifestazione per pace, lavoro e sicurezza” - Il Giorno</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Sala: "Io al Remigration summit? Salvini provoca, ma sono tranquillissimo" - Affaritaliani</t>
+          <t>Sciopero Atm durante la Milano Design Week: ecco le fasce garantite - - Il Gazzettino Metropolitano</t>
         </is>
       </c>
     </row>
